--- a/data/Scheduling.xlsx
+++ b/data/Scheduling.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20390"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Todd\OneDrive - University of Utah\Documents\courses\OperationsResearchforSystems6184\Projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ngc-my.sharepoint.us/personal/joel_wood_ngc_com/Documents/Desktop/Coding/OperationsResearch/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_097F9B7762D2178DB495E0C4537AB5FF08362250" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{14E07359-AD4B-406F-B8C5-5A3678C98A6A}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_097F9B7762D2178DB495E0C4537AB5FF08362250" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B3FE4CB-48E1-4E27-96B4-57E86682439B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29760" yWindow="1050" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees Requests" sheetId="1" r:id="rId1"/>
@@ -1223,12 +1223,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CW87"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>101</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="3" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>199</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>200</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>201</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>202</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>203</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>204</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>205</v>
       </c>
@@ -3973,12 +3973,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="11" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>207</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>208</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>209</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>210</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>211</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>212</v>
       </c>
@@ -5808,7 +5808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>213</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>214</v>
       </c>
@@ -6418,7 +6418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>215</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>216</v>
       </c>
@@ -7028,7 +7028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>217</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>218</v>
       </c>
@@ -7638,7 +7638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>219</v>
       </c>
@@ -7943,7 +7943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>220</v>
       </c>
@@ -8248,7 +8248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>221</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>222</v>
       </c>
@@ -8858,7 +8858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>223</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>224</v>
       </c>
@@ -9468,7 +9468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>225</v>
       </c>
@@ -9773,7 +9773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>226</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:101" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>227</v>
       </c>
@@ -10383,7 +10383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>228</v>
       </c>
@@ -10688,7 +10688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>229</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>230</v>
       </c>
@@ -11298,7 +11298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>231</v>
       </c>
@@ -11603,7 +11603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>232</v>
       </c>
@@ -11908,7 +11908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>233</v>
       </c>
@@ -12213,7 +12213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>234</v>
       </c>
@@ -12518,7 +12518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>235</v>
       </c>
@@ -12823,7 +12823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>236</v>
       </c>
@@ -13128,7 +13128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>237</v>
       </c>
@@ -13433,7 +13433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>238</v>
       </c>
@@ -13738,7 +13738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>239</v>
       </c>
@@ -14043,7 +14043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>240</v>
       </c>
@@ -14348,7 +14348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>241</v>
       </c>
@@ -14653,7 +14653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>242</v>
       </c>
@@ -14958,7 +14958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>243</v>
       </c>
@@ -15263,7 +15263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>244</v>
       </c>
@@ -15568,7 +15568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>245</v>
       </c>
@@ -15873,7 +15873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>246</v>
       </c>
@@ -16178,7 +16178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>247</v>
       </c>
@@ -16483,7 +16483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>248</v>
       </c>
@@ -16788,7 +16788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>249</v>
       </c>
@@ -17093,7 +17093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>250</v>
       </c>
@@ -17398,7 +17398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>251</v>
       </c>
@@ -17703,7 +17703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>252</v>
       </c>
@@ -18008,7 +18008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>253</v>
       </c>
@@ -18313,7 +18313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>254</v>
       </c>
@@ -18618,7 +18618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>255</v>
       </c>
@@ -18923,7 +18923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>256</v>
       </c>
@@ -19228,7 +19228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>257</v>
       </c>
@@ -19533,7 +19533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>258</v>
       </c>
@@ -19838,7 +19838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>259</v>
       </c>
@@ -20143,7 +20143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>260</v>
       </c>
@@ -20448,7 +20448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>261</v>
       </c>
@@ -20753,7 +20753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>262</v>
       </c>
@@ -21058,7 +21058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>263</v>
       </c>
@@ -21363,7 +21363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>264</v>
       </c>
@@ -21668,7 +21668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>265</v>
       </c>
@@ -21973,7 +21973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>266</v>
       </c>
@@ -22278,7 +22278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>267</v>
       </c>
@@ -22583,7 +22583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>268</v>
       </c>
@@ -22888,7 +22888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>269</v>
       </c>
@@ -23193,7 +23193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>270</v>
       </c>
@@ -23498,7 +23498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>271</v>
       </c>
@@ -23803,7 +23803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>272</v>
       </c>
@@ -24108,7 +24108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>273</v>
       </c>
@@ -24413,7 +24413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>274</v>
       </c>
@@ -24718,7 +24718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>275</v>
       </c>
@@ -25023,7 +25023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>276</v>
       </c>
@@ -25328,7 +25328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>277</v>
       </c>
@@ -25633,7 +25633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>278</v>
       </c>
@@ -25938,7 +25938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>279</v>
       </c>
@@ -26243,7 +26243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>280</v>
       </c>
@@ -26548,7 +26548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>281</v>
       </c>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>282</v>
       </c>
@@ -27158,7 +27158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:101" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>283</v>
       </c>
@@ -27471,9 +27471,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F78"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>284</v>
       </c>
@@ -27493,7 +27493,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>207</v>
       </c>
@@ -27513,7 +27513,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>208</v>
       </c>
@@ -27533,7 +27533,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>209</v>
       </c>
@@ -27553,7 +27553,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>210</v>
       </c>
@@ -27573,7 +27573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>211</v>
       </c>
@@ -27593,7 +27593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>212</v>
       </c>
@@ -27613,7 +27613,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>213</v>
       </c>
@@ -27633,7 +27633,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>214</v>
       </c>
@@ -27653,7 +27653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>215</v>
       </c>
@@ -27673,7 +27673,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>216</v>
       </c>
@@ -27693,7 +27693,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>217</v>
       </c>
@@ -27713,7 +27713,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>218</v>
       </c>
@@ -27733,7 +27733,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>219</v>
       </c>
@@ -27753,7 +27753,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>220</v>
       </c>
@@ -27773,7 +27773,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>221</v>
       </c>
@@ -27793,7 +27793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>222</v>
       </c>
@@ -27813,7 +27813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>223</v>
       </c>
@@ -27833,7 +27833,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>224</v>
       </c>
@@ -27853,7 +27853,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>225</v>
       </c>
@@ -27873,7 +27873,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>226</v>
       </c>
@@ -27893,7 +27893,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>227</v>
       </c>
@@ -27913,7 +27913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>228</v>
       </c>
@@ -27933,7 +27933,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>229</v>
       </c>
@@ -27953,7 +27953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>230</v>
       </c>
@@ -27973,7 +27973,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>231</v>
       </c>
@@ -27993,7 +27993,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>232</v>
       </c>
@@ -28013,7 +28013,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>233</v>
       </c>
@@ -28033,7 +28033,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>234</v>
       </c>
@@ -28053,7 +28053,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>235</v>
       </c>
@@ -28073,7 +28073,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>236</v>
       </c>
@@ -28093,7 +28093,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>237</v>
       </c>
@@ -28113,7 +28113,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>238</v>
       </c>
@@ -28133,7 +28133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>239</v>
       </c>
@@ -28153,7 +28153,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>240</v>
       </c>
@@ -28173,7 +28173,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>241</v>
       </c>
@@ -28193,7 +28193,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>242</v>
       </c>
@@ -28213,7 +28213,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>243</v>
       </c>
@@ -28233,7 +28233,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>244</v>
       </c>
@@ -28253,7 +28253,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>245</v>
       </c>
@@ -28273,7 +28273,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>246</v>
       </c>
@@ -28293,7 +28293,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>247</v>
       </c>
@@ -28313,7 +28313,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>248</v>
       </c>
@@ -28333,7 +28333,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>249</v>
       </c>
@@ -28353,7 +28353,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>250</v>
       </c>
@@ -28373,7 +28373,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>251</v>
       </c>
@@ -28393,7 +28393,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>252</v>
       </c>
@@ -28413,7 +28413,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>253</v>
       </c>
@@ -28433,7 +28433,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>254</v>
       </c>
@@ -28453,7 +28453,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>255</v>
       </c>
@@ -28473,7 +28473,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>256</v>
       </c>
@@ -28493,7 +28493,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>257</v>
       </c>
@@ -28513,7 +28513,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>258</v>
       </c>
@@ -28533,7 +28533,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>259</v>
       </c>
@@ -28553,7 +28553,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>260</v>
       </c>
@@ -28573,7 +28573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>261</v>
       </c>
@@ -28593,7 +28593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>262</v>
       </c>
@@ -28613,7 +28613,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>263</v>
       </c>
@@ -28633,7 +28633,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>264</v>
       </c>
@@ -28653,7 +28653,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>265</v>
       </c>
@@ -28673,7 +28673,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>266</v>
       </c>
@@ -28693,7 +28693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>267</v>
       </c>
@@ -28713,7 +28713,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>268</v>
       </c>
@@ -28733,7 +28733,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>269</v>
       </c>
@@ -28753,7 +28753,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>270</v>
       </c>
@@ -28773,7 +28773,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>271</v>
       </c>
@@ -28793,7 +28793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>272</v>
       </c>
@@ -28813,7 +28813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>273</v>
       </c>
@@ -28833,7 +28833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>274</v>
       </c>
@@ -28853,7 +28853,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>275</v>
       </c>
@@ -28873,7 +28873,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>276</v>
       </c>
@@ -28893,7 +28893,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>277</v>
       </c>
@@ -28913,7 +28913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>278</v>
       </c>
@@ -28933,7 +28933,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>279</v>
       </c>
@@ -28953,7 +28953,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>280</v>
       </c>
@@ -28973,7 +28973,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>281</v>
       </c>
@@ -28993,7 +28993,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>282</v>
       </c>
@@ -29013,7 +29013,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>283</v>
       </c>
@@ -29041,7 +29041,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
